--- a/BEAST2/Data/Pterosaur ages_11-23.xlsx
+++ b/BEAST2/Data/Pterosaur ages_11-23.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\revbayes-v1.2.1-win64\revbayes-v1.2.1\Files\PterosaurPhylogeny\BEAST2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B13142-F474-4F31-A60D-351A1947AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB5ECE3-881C-4AF4-B4DD-9CAF97BE99E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Defined ages" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="259">
   <si>
     <t>Age</t>
   </si>
@@ -575,9 +575,6 @@
     <t>Eudimorphodon ranzii -2</t>
   </si>
   <si>
-    <t>Preondactylus buffarinii -1</t>
-  </si>
-  <si>
     <t>Rhamphorhynchus muensteri - 1</t>
   </si>
   <si>
@@ -816,6 +813,12 @@
   </si>
   <si>
     <t>Carniadactylus rosenfeldi -1</t>
+  </si>
+  <si>
+    <t>(Wild 1978)</t>
+  </si>
+  <si>
+    <t>Riva di solto</t>
   </si>
 </sst>
 </file>
@@ -855,7 +858,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -948,12 +951,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEF05E9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1016,7 +1013,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1044,15 +1041,14 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1651,145 +1647,146 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="22" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="22" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="22" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="22" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="22" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="22" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="22" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="23" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="23" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="23" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="23" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="23" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="24" t="s">
+      <c r="A44" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B44" s="24" t="s">
+      <c r="B44" s="23" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B47" s="23" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="B47" s="24" t="s">
-        <v>199</v>
-      </c>
-    </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B49" s="24" t="s">
+      <c r="A49" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" s="23" t="s">
         <v>207</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="B50" s="24" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1849,10 +1846,10 @@
       <c r="B2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="30" t="s">
         <v>58</v>
       </c>
       <c r="E2" s="12">
@@ -1884,10 +1881,10 @@
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="30" t="s">
         <v>72</v>
       </c>
       <c r="E3" s="15">
@@ -1896,14 +1893,14 @@
       <c r="F3" s="15">
         <v>209.51</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="24" t="s">
         <v>76</v>
       </c>
       <c r="H3" t="s">
         <v>71</v>
       </c>
       <c r="I3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>67</v>
@@ -1919,10 +1916,10 @@
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="30" t="s">
         <v>72</v>
       </c>
       <c r="E4" s="15">
@@ -1931,14 +1928,14 @@
       <c r="F4" s="15">
         <v>209.51</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="24" t="s">
         <v>76</v>
       </c>
       <c r="H4" t="s">
         <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>69</v>
@@ -1954,10 +1951,10 @@
       <c r="B5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="30" t="s">
         <v>81</v>
       </c>
       <c r="E5" s="15">
@@ -1989,10 +1986,10 @@
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="30" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="14">
@@ -2019,15 +2016,15 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="30" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="14">
@@ -2059,10 +2056,10 @@
       <c r="B8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="30" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="17">
@@ -2071,19 +2068,19 @@
       <c r="F8" s="17">
         <v>199.46</v>
       </c>
-      <c r="G8" s="29" t="s">
-        <v>189</v>
+      <c r="G8" s="28" t="s">
+        <v>188</v>
       </c>
       <c r="H8" t="s">
+        <v>186</v>
+      </c>
+      <c r="I8" t="s">
         <v>187</v>
       </c>
-      <c r="I8" t="s">
-        <v>188</v>
-      </c>
-      <c r="K8" s="27" t="s">
+      <c r="K8" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="L8" s="27" t="s">
+      <c r="L8" s="26" t="s">
         <v>163</v>
       </c>
     </row>
@@ -2094,10 +2091,10 @@
       <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="30" t="s">
         <v>5</v>
       </c>
       <c r="E9" s="14">
@@ -2116,10 +2113,10 @@
         <v>97</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="L9" s="16" t="s">
         <v>190</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -2143,19 +2140,19 @@
         <v>227.3</v>
       </c>
       <c r="G10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H10" t="s">
         <v>120</v>
       </c>
       <c r="I10" t="s">
-        <v>211</v>
-      </c>
-      <c r="K10" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="L10" s="28" t="s">
         <v>192</v>
-      </c>
-      <c r="L10" s="29" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -2178,7 +2175,7 @@
         <v>209.51</v>
       </c>
       <c r="G11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H11" t="s">
         <v>119</v>
@@ -2186,8 +2183,8 @@
       <c r="I11" t="s">
         <v>119</v>
       </c>
-      <c r="K11" s="26"/>
-      <c r="L11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="24"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -2196,10 +2193,10 @@
       <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="30" t="s">
         <v>72</v>
       </c>
       <c r="E12" s="15">
@@ -2209,16 +2206,16 @@
         <v>214.03</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
         <v>103</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
+        <v>183</v>
+      </c>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -2248,8 +2245,8 @@
       <c r="I13" t="s">
         <v>101</v>
       </c>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -2258,10 +2255,10 @@
       <c r="B14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="14">
@@ -2279,8 +2276,8 @@
       <c r="I14" t="s">
         <v>101</v>
       </c>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2310,8 +2307,8 @@
       <c r="I15" t="s">
         <v>110</v>
       </c>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -2341,8 +2338,8 @@
       <c r="I16" t="s">
         <v>115</v>
       </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
@@ -2351,10 +2348,10 @@
       <c r="B17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="30" t="s">
         <v>5</v>
       </c>
       <c r="E17" s="14">
@@ -2372,8 +2369,8 @@
       <c r="I17" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
@@ -2382,60 +2379,60 @@
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>84</v>
+      <c r="D18" s="30" t="s">
+        <v>72</v>
       </c>
       <c r="E18" s="15">
         <v>217.49</v>
       </c>
-      <c r="F18" s="14">
-        <v>209.51</v>
+      <c r="F18" s="15">
+        <v>214.03</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H18" t="s">
-        <v>124</v>
+        <v>257</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
+        <v>182</v>
+      </c>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="30" t="s">
-        <v>177</v>
+      <c r="A19" s="29" t="s">
+        <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="15">
-        <v>217.49</v>
-      </c>
-      <c r="F19" s="15">
+      <c r="C19" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="14">
         <v>214.03</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>180</v>
+      <c r="F19" s="14">
+        <v>209.51</v>
+      </c>
+      <c r="G19" t="s">
+        <v>92</v>
       </c>
       <c r="H19" t="s">
         <v>124</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
+        <v>185</v>
+      </c>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -2465,8 +2462,8 @@
       <c r="I20" t="s">
         <v>107</v>
       </c>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
@@ -2496,12 +2493,12 @@
       <c r="I21" t="s">
         <v>128</v>
       </c>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
     </row>
     <row r="22" spans="1:12" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>28</v>
@@ -2519,17 +2516,17 @@
       <c r="F22" s="20">
         <v>149.24</v>
       </c>
-      <c r="G22" s="28" t="s">
+      <c r="G22" s="27" t="s">
         <v>135</v>
       </c>
       <c r="H22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I22" t="s">
-        <v>201</v>
-      </c>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
+        <v>200</v>
+      </c>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
@@ -2559,8 +2556,8 @@
       <c r="I23" t="s">
         <v>131</v>
       </c>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
@@ -2569,10 +2566,10 @@
       <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="30" t="s">
         <v>84</v>
       </c>
       <c r="E24" s="15">
@@ -2590,8 +2587,8 @@
       <c r="I24" t="s">
         <v>94</v>
       </c>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
     </row>
     <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="18" t="s">
@@ -2600,10 +2597,10 @@
       <c r="B25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="27" t="s">
         <v>98</v>
       </c>
       <c r="E25" s="14">
@@ -2621,8 +2618,8 @@
       <c r="I25" t="s">
         <v>101</v>
       </c>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
@@ -2631,10 +2628,10 @@
       <c r="B26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="30" t="s">
         <v>5</v>
       </c>
       <c r="E26" s="14">
@@ -2652,16 +2649,16 @@
       <c r="I26" t="s">
         <v>97</v>
       </c>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F26">
@@ -2722,10 +2719,10 @@
       <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="30" t="s">
         <v>84</v>
       </c>
       <c r="E2" s="14">
@@ -2741,36 +2738,36 @@
         <v>93</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="14">
+      <c r="C3" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="15">
+        <v>217.49</v>
+      </c>
+      <c r="F3" s="15">
         <v>214.03</v>
       </c>
-      <c r="F3" s="14">
-        <v>209.51</v>
-      </c>
       <c r="G3" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H3" t="s">
         <v>93</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>87</v>
@@ -2799,13 +2796,13 @@
         <v>209.51</v>
       </c>
       <c r="G4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -2828,13 +2825,13 @@
         <v>209.51</v>
       </c>
       <c r="G5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -2845,10 +2842,10 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E6" s="20">
         <f>F5</f>
@@ -2858,13 +2855,13 @@
         <v>201.36</v>
       </c>
       <c r="G6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -2874,11 +2871,11 @@
       <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>196</v>
+      <c r="D7" s="30" t="s">
+        <v>195</v>
       </c>
       <c r="E7" s="17">
         <v>201.36</v>
@@ -2886,14 +2883,14 @@
       <c r="F7" s="13">
         <v>196.18</v>
       </c>
-      <c r="G7" s="28" t="s">
-        <v>200</v>
+      <c r="G7" s="27" t="s">
+        <v>199</v>
       </c>
       <c r="H7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I7" t="s">
         <v>194</v>
-      </c>
-      <c r="I7" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2903,10 +2900,10 @@
       <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="30" t="s">
         <v>84</v>
       </c>
       <c r="E8" s="14">
@@ -2916,27 +2913,27 @@
         <v>209.51</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E9" s="13">
         <v>149.24</v>
@@ -2945,13 +2942,13 @@
         <v>146.16999999999999</v>
       </c>
       <c r="G9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H9" t="s">
         <v>204</v>
       </c>
-      <c r="H9" t="s">
-        <v>205</v>
-      </c>
       <c r="I9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2997,7 +2994,7 @@
         <v>237</v>
       </c>
       <c r="D3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:F7" si="0">B3-143.1</f>
@@ -3107,7 +3104,7 @@
         <v>233.67</v>
       </c>
       <c r="D9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E9">
         <f>B9-146.17</f>
@@ -3188,7 +3185,7 @@
         <v>32.590000000000003</v>
       </c>
       <c r="I2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -3221,7 +3218,7 @@
         <v>71.320000000000022</v>
       </c>
       <c r="I3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -3254,7 +3251,7 @@
         <v>71.320000000000022</v>
       </c>
       <c r="I4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3287,7 +3284,7 @@
         <v>13.100000000000023</v>
       </c>
       <c r="I5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -3320,7 +3317,7 @@
         <v>67.860000000000014</v>
       </c>
       <c r="I6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -3353,7 +3350,7 @@
         <v>67.860000000000014</v>
       </c>
       <c r="I7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -3385,6 +3382,9 @@
         <f t="shared" si="3"/>
         <v>55.190000000000026</v>
       </c>
+      <c r="I8" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -3415,6 +3415,9 @@
         <f t="shared" si="3"/>
         <v>67.860000000000014</v>
       </c>
+      <c r="I9" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -3505,6 +3508,9 @@
         <f t="shared" si="3"/>
         <v>71.320000000000022</v>
       </c>
+      <c r="I12" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -3655,6 +3661,9 @@
         <f t="shared" si="3"/>
         <v>67.860000000000014</v>
       </c>
+      <c r="I17" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
@@ -3666,25 +3675,28 @@
       <c r="C18" s="15">
         <v>217.49</v>
       </c>
-      <c r="D18" s="14">
-        <v>209.51</v>
+      <c r="D18" s="15">
+        <v>214.03</v>
       </c>
       <c r="E18">
         <f t="shared" si="0"/>
-        <v>213.5</v>
+        <v>215.76</v>
       </c>
       <c r="F18">
         <f t="shared" si="1"/>
-        <v>67.330000000000013</v>
+        <v>69.59</v>
       </c>
       <c r="G18">
         <f t="shared" si="2"/>
-        <v>63.34</v>
+        <v>67.860000000000014</v>
       </c>
       <c r="H18">
         <f t="shared" si="3"/>
         <v>71.320000000000022</v>
       </c>
+      <c r="I18" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
@@ -3693,27 +3705,30 @@
       <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="15">
-        <v>217.49</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="14">
         <v>214.03</v>
+      </c>
+      <c r="D19" s="14">
+        <v>209.51</v>
       </c>
       <c r="E19">
         <f t="shared" si="0"/>
-        <v>215.76</v>
+        <v>211.76999999999998</v>
       </c>
       <c r="F19">
         <f t="shared" si="1"/>
-        <v>69.59</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="G19">
         <f t="shared" si="2"/>
-        <v>67.860000000000014</v>
+        <v>63.34</v>
       </c>
       <c r="H19">
         <f t="shared" si="3"/>
-        <v>71.320000000000022</v>
+        <v>67.860000000000014</v>
+      </c>
+      <c r="I19" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3867,7 +3882,7 @@
         <v>71.320000000000022</v>
       </c>
       <c r="I24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3928,6 +3943,9 @@
       <c r="H26">
         <f t="shared" si="3"/>
         <v>67.860000000000014</v>
+      </c>
+      <c r="I26" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3975,7 +3993,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -4003,42 +4021,45 @@
         <v>67.860000000000014</v>
       </c>
       <c r="I2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="15">
+        <v>217.49</v>
+      </c>
+      <c r="D3" s="15">
         <v>214.03</v>
-      </c>
-      <c r="D3" s="14">
-        <v>209.51</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E5" si="0">(C3+D3)/2</f>
-        <v>211.76999999999998</v>
+        <v>215.76</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F5" si="1">E3-146.17</f>
-        <v>65.599999999999994</v>
+        <v>69.59</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G4" si="2">D3-146.17</f>
-        <v>63.34</v>
+        <v>67.860000000000014</v>
       </c>
       <c r="H3">
         <f t="shared" ref="H3:H4" si="3">C3-146.17</f>
-        <v>67.860000000000014</v>
+        <v>71.320000000000022</v>
+      </c>
+      <c r="I3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
@@ -4068,7 +4089,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>30</v>
@@ -4088,17 +4109,17 @@
         <v>67.330000000000013</v>
       </c>
       <c r="G5">
-        <f t="shared" ref="G3:G5" si="4">D5-146.17</f>
+        <f t="shared" ref="G5" si="4">D5-146.17</f>
         <v>63.34</v>
       </c>
       <c r="H5">
-        <f t="shared" ref="H4:H9" si="5">C5-146.17</f>
+        <f t="shared" ref="H5:H9" si="5">C5-146.17</f>
         <v>71.320000000000022</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>30</v>
@@ -4110,15 +4131,15 @@
         <v>201.36</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E4:E9" si="6">(C6+D6)/2</f>
+        <f t="shared" ref="E6:E9" si="6">(C6+D6)/2</f>
         <v>205.435</v>
       </c>
       <c r="F6">
-        <f t="shared" ref="F4:F9" si="7">E6-146.17</f>
+        <f t="shared" ref="F6:F9" si="7">E6-146.17</f>
         <v>59.265000000000015</v>
       </c>
       <c r="G6">
-        <f t="shared" ref="G4:G9" si="8">D6-146.17</f>
+        <f t="shared" ref="G6:G9" si="8">D6-146.17</f>
         <v>55.190000000000026</v>
       </c>
       <c r="H6">
@@ -4128,7 +4149,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>28</v>
@@ -4155,10 +4176,13 @@
         <f t="shared" si="5"/>
         <v>55.190000000000026</v>
       </c>
+      <c r="I7" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -4185,10 +4209,13 @@
         <f t="shared" si="5"/>
         <v>67.860000000000014</v>
       </c>
+      <c r="I8" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -4231,7 +4258,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1">
         <v>26.615000000000009</v>
@@ -4239,7 +4266,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B2">
         <v>67.330000000000013</v>
@@ -4247,7 +4274,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B3">
         <v>65.599999999999994</v>
@@ -4255,7 +4282,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B4">
         <v>10.855000000000018</v>
@@ -4263,7 +4290,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B5">
         <v>61.525000000000006</v>
@@ -4271,7 +4298,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B6">
         <v>67.330000000000013</v>
@@ -4279,7 +4306,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B7">
         <v>54.240000000000038</v>
@@ -4287,7 +4314,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B8">
         <v>61.525000000000006</v>
@@ -4295,7 +4322,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B9">
         <v>68.160000000000025</v>
@@ -4303,7 +4330,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B10">
         <v>72.235000000000014</v>
@@ -4311,7 +4338,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B11">
         <v>69.59</v>
@@ -4319,7 +4346,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B12">
         <v>75.284999999999997</v>
@@ -4327,7 +4354,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13">
         <v>84.28</v>
@@ -4335,7 +4362,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B14">
         <v>90.37</v>
@@ -4343,7 +4370,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B15">
         <v>88.830000000000013</v>
@@ -4351,7 +4378,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B16">
         <v>61.525000000000006</v>
@@ -4359,7 +4386,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B17">
         <v>67.330000000000013</v>
@@ -4367,7 +4394,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B18">
         <v>69.59</v>
@@ -4375,7 +4402,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B19">
         <v>83.180000000000035</v>
@@ -4383,7 +4410,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B20">
         <v>63.565000000000026</v>
@@ -4391,7 +4418,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B21">
         <v>31.170000000000016</v>
@@ -4399,7 +4426,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B22">
         <v>79.375000000000028</v>
@@ -4407,7 +4434,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B23">
         <v>67.330000000000013</v>
@@ -4415,7 +4442,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B24">
         <v>84.28</v>
@@ -4423,7 +4450,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B25">
         <v>61.525000000000006</v>
@@ -4431,7 +4458,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B26">
         <v>65.599999999999994</v>
@@ -4439,7 +4466,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B27">
         <v>72.235000000000014</v>
@@ -4447,7 +4474,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B28">
         <v>67.330000000000013</v>
@@ -4455,7 +4482,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B29">
         <v>59.265000000000015</v>
@@ -4463,7 +4490,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B30">
         <v>52.600000000000023</v>
@@ -4471,7 +4498,7 @@
     </row>
     <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B31">
         <v>65.599999999999994</v>
@@ -4479,7 +4506,7 @@
     </row>
     <row r="32" spans="1:2" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B32">
         <v>0</v>
